--- a/docs/collections/ogai/metadata/data.xlsx
+++ b/docs/collections/ogai/metadata/data.xlsx
@@ -3393,10 +3393,10 @@
     <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/56663d54-d9ac-4d9d-b4fe-7fb7d64a6f21/manifest</t>
   </si>
   <si>
-    <t>肥後國志(ヒゴ コクシ) / 森本一瑞著 ; 水島貫之校補. [写本]</t>
-  </si>
-  <si>
-    <t>ヒゴ コクシ</t>
+    <t>肥後國志略(ヒゴ コクシリャク) / 森本一瑞謹誌. [写本]</t>
+  </si>
+  <si>
+    <t>ヒゴ コクシリャク</t>
   </si>
   <si>
     <t>[書写地不明] : [書写者不明], [1---] 1冊 ; 27cm 別書名: 肥後国志 ; 肥後國志略 注記: 写本,和装,袋綴本 ; 1:序,凡例,図</t>

--- a/docs/collections/ogai/metadata/data.xlsx
+++ b/docs/collections/ogai/metadata/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF354"/>
+  <dimension ref="A1:AF380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>21901</v>
+        <v>23896</v>
       </c>
     </row>
     <row r="3">
@@ -40891,6 +40891,3130 @@
         <v>60</v>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>[源氏物語] [1]</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6407ca58-3674-4336-1374-6e8c30058b9e.json</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>6407ca58-3674-4336-1374-6e8c30058b9e</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr"/>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/6407ca58-3674-4336-1374-6e8c30058b9e</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/525d97f743a67560b50194aa9171f09a04d43ad0.jpg</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381440</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr"/>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr"/>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6407ca58-3674-4336-1374-6e8c30058b9e/manifest</t>
+        </is>
+      </c>
+      <c r="AB355" t="inlineStr"/>
+      <c r="AC355" t="inlineStr"/>
+      <c r="AD355" t="inlineStr"/>
+      <c r="AE355" t="inlineStr"/>
+      <c r="AF355" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>[源氏物語] [2]</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0f11a3ed-18c2-7322-6340-19ed3f0d966e.json</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>0f11a3ed-18c2-7322-6340-19ed3f0d966e</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr"/>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/0f11a3ed-18c2-7322-6340-19ed3f0d966e</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c345e5c539f6f7dc4b0916f038803fb8ead3663f.jpg</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381439</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr"/>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr"/>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0f11a3ed-18c2-7322-6340-19ed3f0d966e/manifest</t>
+        </is>
+      </c>
+      <c r="AB356" t="inlineStr"/>
+      <c r="AC356" t="inlineStr"/>
+      <c r="AD356" t="inlineStr"/>
+      <c r="AE356" t="inlineStr"/>
+      <c r="AF356" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>[源氏物語] [3]</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/691a4ca3-80ce-4112-1521-7fa61ff95bd0.json</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>691a4ca3-80ce-4112-1521-7fa61ff95bd0</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr"/>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/691a4ca3-80ce-4112-1521-7fa61ff95bd0</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f3c0668d922298b5c00e02b705bed90e1dd0b1c6.jpg</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381438</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr"/>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr"/>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/691a4ca3-80ce-4112-1521-7fa61ff95bd0/manifest</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr"/>
+      <c r="AC357" t="inlineStr"/>
+      <c r="AD357" t="inlineStr"/>
+      <c r="AE357" t="inlineStr"/>
+      <c r="AF357" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>[源氏物語] [4]</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b90bbddc-509d-7c12-0fb9-af409a90a487.json</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>b90bbddc-509d-7c12-0fb9-af409a90a487</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr"/>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/b90bbddc-509d-7c12-0fb9-af409a90a487</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/33ed00e2e9167ff1291684af83196bf2fcd3a56e.jpg</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381437</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr"/>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr"/>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b90bbddc-509d-7c12-0fb9-af409a90a487/manifest</t>
+        </is>
+      </c>
+      <c r="AB358" t="inlineStr"/>
+      <c r="AC358" t="inlineStr"/>
+      <c r="AD358" t="inlineStr"/>
+      <c r="AE358" t="inlineStr"/>
+      <c r="AF358" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>[源氏物語] [5]</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/11670e65-1484-8b2f-6dc8-81490cb898ab.json</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>11670e65-1484-8b2f-6dc8-81490cb898ab</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr"/>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/11670e65-1484-8b2f-6dc8-81490cb898ab</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8cd46f21e3fd25c50b17cffd6eda7a31ce450e58.jpg</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381436</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr"/>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr"/>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/11670e65-1484-8b2f-6dc8-81490cb898ab/manifest</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr"/>
+      <c r="AC359" t="inlineStr"/>
+      <c r="AD359" t="inlineStr"/>
+      <c r="AE359" t="inlineStr"/>
+      <c r="AF359" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>[源氏物語] [6]</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4ef9d926-92b0-55b7-2d63-cfe3a6642da4.json</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>4ef9d926-92b0-55b7-2d63-cfe3a6642da4</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr"/>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/4ef9d926-92b0-55b7-2d63-cfe3a6642da4</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/46dae9365273018e02f05180d3a4498a1d93d6a5.jpg</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381435</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr"/>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr"/>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4ef9d926-92b0-55b7-2d63-cfe3a6642da4/manifest</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr"/>
+      <c r="AC360" t="inlineStr"/>
+      <c r="AD360" t="inlineStr"/>
+      <c r="AE360" t="inlineStr"/>
+      <c r="AF360" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>[源氏物語] [7]</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6492697e-0977-37cb-36ee-fa78ae187595.json</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>6492697e-0977-37cb-36ee-fa78ae187595</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr"/>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/6492697e-0977-37cb-36ee-fa78ae187595</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/73921b56a4dedac3a400752391ce40d55b897fdf.jpg</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381434</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr"/>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr"/>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6492697e-0977-37cb-36ee-fa78ae187595/manifest</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr"/>
+      <c r="AC361" t="inlineStr"/>
+      <c r="AD361" t="inlineStr"/>
+      <c r="AE361" t="inlineStr"/>
+      <c r="AF361" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>[源氏物語] [8]</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fce3be19-8c15-6ebd-9461-67a7b6de7b25.json</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>fce3be19-8c15-6ebd-9461-67a7b6de7b25</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr"/>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/fce3be19-8c15-6ebd-9461-67a7b6de7b25</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a0b21947b49be906f8b513816ef7be5196467a3b.jpg</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381433</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr"/>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr"/>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fce3be19-8c15-6ebd-9461-67a7b6de7b25/manifest</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr"/>
+      <c r="AC362" t="inlineStr"/>
+      <c r="AD362" t="inlineStr"/>
+      <c r="AE362" t="inlineStr"/>
+      <c r="AF362" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>[源氏物語] [9]</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0f031b59-a6ec-9689-981e-141a09613a81.json</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>0f031b59-a6ec-9689-981e-141a09613a81</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr"/>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/0f031b59-a6ec-9689-981e-141a09613a81</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4d46eff0dda7349f1b7722b8a4761c63ac98b8a3.jpg</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381432</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr"/>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr"/>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0f031b59-a6ec-9689-981e-141a09613a81/manifest</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr"/>
+      <c r="AC363" t="inlineStr"/>
+      <c r="AD363" t="inlineStr"/>
+      <c r="AE363" t="inlineStr"/>
+      <c r="AF363" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>[源氏物語] [10]</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a3729f7a-0b0f-3d39-2d4f-8b4bc439222c.json</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>a3729f7a-0b0f-3d39-2d4f-8b4bc439222c</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr"/>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/a3729f7a-0b0f-3d39-2d4f-8b4bc439222c</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c375a8b4bab3cac0dc72fb26ad2af1666c7ab83a.jpg</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381431</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr"/>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr"/>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a3729f7a-0b0f-3d39-2d4f-8b4bc439222c/manifest</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr"/>
+      <c r="AC364" t="inlineStr"/>
+      <c r="AD364" t="inlineStr"/>
+      <c r="AE364" t="inlineStr"/>
+      <c r="AF364" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>[源氏物語] [11]</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5daa3f84-6b9c-54b3-2f78-9275b9cb6e3b.json</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>5daa3f84-6b9c-54b3-2f78-9275b9cb6e3b</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr"/>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/5daa3f84-6b9c-54b3-2f78-9275b9cb6e3b</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d77787876a9a7a245694fcd93ab781ce6a8a12c1.jpg</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381430</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr"/>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr"/>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5daa3f84-6b9c-54b3-2f78-9275b9cb6e3b/manifest</t>
+        </is>
+      </c>
+      <c r="AB365" t="inlineStr"/>
+      <c r="AC365" t="inlineStr"/>
+      <c r="AD365" t="inlineStr"/>
+      <c r="AE365" t="inlineStr"/>
+      <c r="AF365" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>[源氏物語] [12]</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/81e29354-71bd-024e-14dd-d9f7faa425a7.json</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>81e29354-71bd-024e-14dd-d9f7faa425a7</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr"/>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/81e29354-71bd-024e-14dd-d9f7faa425a7</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/438d244b2552f5513048a82fb37ccd1d690e9bb4.jpg</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381429</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W366" t="inlineStr"/>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="Z366" t="inlineStr"/>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/81e29354-71bd-024e-14dd-d9f7faa425a7/manifest</t>
+        </is>
+      </c>
+      <c r="AB366" t="inlineStr"/>
+      <c r="AC366" t="inlineStr"/>
+      <c r="AD366" t="inlineStr"/>
+      <c r="AE366" t="inlineStr"/>
+      <c r="AF366" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>[源氏物語] [13]</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6dec4cbf-827b-4817-2add-13f0535f7186.json</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>6dec4cbf-827b-4817-2add-13f0535f7186</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr"/>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/6dec4cbf-827b-4817-2add-13f0535f7186</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7e2ac9a859858c239ad46c7431376adb8e19605e.jpg</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381428</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr"/>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr"/>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6dec4cbf-827b-4817-2add-13f0535f7186/manifest</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr"/>
+      <c r="AC367" t="inlineStr"/>
+      <c r="AD367" t="inlineStr"/>
+      <c r="AE367" t="inlineStr"/>
+      <c r="AF367" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>[源氏物語] [14]</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bddf1283-6896-5ab2-3284-ff08458d257d.json</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>bddf1283-6896-5ab2-3284-ff08458d257d</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr"/>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/bddf1283-6896-5ab2-3284-ff08458d257d</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac6d3f223631453b60d6f017aaa7304e193f447e.jpg</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381427</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr"/>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr"/>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bddf1283-6896-5ab2-3284-ff08458d257d/manifest</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr"/>
+      <c r="AC368" t="inlineStr"/>
+      <c r="AD368" t="inlineStr"/>
+      <c r="AE368" t="inlineStr"/>
+      <c r="AF368" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>[源氏物語] [15]</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4784d0c9-2dc3-6ee5-73fa-bbc854547307.json</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>4784d0c9-2dc3-6ee5-73fa-bbc854547307</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr"/>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/4784d0c9-2dc3-6ee5-73fa-bbc854547307</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0ac6802404e75f110067069d69191769d659bcdc.jpg</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381426</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr"/>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr"/>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4784d0c9-2dc3-6ee5-73fa-bbc854547307/manifest</t>
+        </is>
+      </c>
+      <c r="AB369" t="inlineStr"/>
+      <c r="AC369" t="inlineStr"/>
+      <c r="AD369" t="inlineStr"/>
+      <c r="AE369" t="inlineStr"/>
+      <c r="AF369" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>[源氏物語] [16]</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/01547123-924a-9d65-93a6-69e4703f4f31.json</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>01547123-924a-9d65-93a6-69e4703f4f31</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr"/>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/01547123-924a-9d65-93a6-69e4703f4f31</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/bde6710618dc1ed1fa3a5b61cb36a2ef9f760f2d.jpg</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381425</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr"/>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="Z370" t="inlineStr"/>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/01547123-924a-9d65-93a6-69e4703f4f31/manifest</t>
+        </is>
+      </c>
+      <c r="AB370" t="inlineStr"/>
+      <c r="AC370" t="inlineStr"/>
+      <c r="AD370" t="inlineStr"/>
+      <c r="AE370" t="inlineStr"/>
+      <c r="AF370" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>[源氏物語] [17]</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f9c63d10-6df6-124b-9adf-429fb95d3776.json</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>f9c63d10-6df6-124b-9adf-429fb95d3776</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr"/>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/f9c63d10-6df6-124b-9adf-429fb95d3776</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/314b5346e9ccf393f5d100c9100be05437034a71.jpg</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381424</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr"/>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr"/>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f9c63d10-6df6-124b-9adf-429fb95d3776/manifest</t>
+        </is>
+      </c>
+      <c r="AB371" t="inlineStr"/>
+      <c r="AC371" t="inlineStr"/>
+      <c r="AD371" t="inlineStr"/>
+      <c r="AE371" t="inlineStr"/>
+      <c r="AF371" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>[源氏物語] [18]</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/190d4766-2b68-5836-251d-1c2f6a5a7c97.json</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>190d4766-2b68-5836-251d-1c2f6a5a7c97</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr"/>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/190d4766-2b68-5836-251d-1c2f6a5a7c97</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5143c1a1b889690702a2a03aea2feba9db064289.jpg</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381423</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr"/>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr"/>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/190d4766-2b68-5836-251d-1c2f6a5a7c97/manifest</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr"/>
+      <c r="AC372" t="inlineStr"/>
+      <c r="AD372" t="inlineStr"/>
+      <c r="AE372" t="inlineStr"/>
+      <c r="AF372" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>[源氏物語] [19]</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/225d47b4-8c2d-73fe-5892-d83df9eb44f5.json</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>225d47b4-8c2d-73fe-5892-d83df9eb44f5</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr"/>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/225d47b4-8c2d-73fe-5892-d83df9eb44f5</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b7478d2bf32337f495e090037767d33c5e1170a4.jpg</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381422</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr"/>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr"/>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/225d47b4-8c2d-73fe-5892-d83df9eb44f5/manifest</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr"/>
+      <c r="AC373" t="inlineStr"/>
+      <c r="AD373" t="inlineStr"/>
+      <c r="AE373" t="inlineStr"/>
+      <c r="AF373" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>[源氏物語] [20]</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9622ecef-1327-2509-1822-ed33f3c56a03.json</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>9622ecef-1327-2509-1822-ed33f3c56a03</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr"/>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/9622ecef-1327-2509-1822-ed33f3c56a03</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b8c2ff3e733456e3c320575f9e94fc04bd8ea5d2.jpg</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381421</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr"/>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr"/>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9622ecef-1327-2509-1822-ed33f3c56a03/manifest</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr"/>
+      <c r="AC374" t="inlineStr"/>
+      <c r="AD374" t="inlineStr"/>
+      <c r="AE374" t="inlineStr"/>
+      <c r="AF374" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>[源氏物語] [21]</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/edeefb01-1805-5115-73b8-040da70e4f4e.json</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>edeefb01-1805-5115-73b8-040da70e4f4e</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr"/>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/edeefb01-1805-5115-73b8-040da70e4f4e</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/166565e9be733366ac839531cb9a809768a5b795.jpg</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381420</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr"/>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr"/>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/edeefb01-1805-5115-73b8-040da70e4f4e/manifest</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr"/>
+      <c r="AC375" t="inlineStr"/>
+      <c r="AD375" t="inlineStr"/>
+      <c r="AE375" t="inlineStr"/>
+      <c r="AF375" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>[源氏物語] [22]</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/594a0229-6960-7b39-31e6-d23c90814497.json</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>594a0229-6960-7b39-31e6-d23c90814497</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr"/>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/594a0229-6960-7b39-31e6-d23c90814497</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8666550cfcca3a10b8c7f68559d13e823c73843b.jpg</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381419</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr"/>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr"/>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/594a0229-6960-7b39-31e6-d23c90814497/manifest</t>
+        </is>
+      </c>
+      <c r="AB376" t="inlineStr"/>
+      <c r="AC376" t="inlineStr"/>
+      <c r="AD376" t="inlineStr"/>
+      <c r="AE376" t="inlineStr"/>
+      <c r="AF376" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>[源氏物語] [23]</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/af7a2462-0118-2462-7079-3874869c211e.json</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>af7a2462-0118-2462-7079-3874869c211e</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr"/>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/af7a2462-0118-2462-7079-3874869c211e</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3be780e5e704e1c042af6ff1cf3280d20bc5c09d.jpg</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381418</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr"/>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr"/>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/af7a2462-0118-2462-7079-3874869c211e/manifest</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr"/>
+      <c r="AC377" t="inlineStr"/>
+      <c r="AD377" t="inlineStr"/>
+      <c r="AE377" t="inlineStr"/>
+      <c r="AF377" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>[源氏物語] [24]</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/60929145-4143-4481-1cf4-49c863029eb4.json</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>60929145-4143-4481-1cf4-49c863029eb4</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr"/>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/60929145-4143-4481-1cf4-49c863029eb4</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/84de8a08e61a22c52d1f5c1a323fcc0bab06618c.jpg</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381417</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr"/>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr"/>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/60929145-4143-4481-1cf4-49c863029eb4/manifest</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr"/>
+      <c r="AC378" t="inlineStr"/>
+      <c r="AD378" t="inlineStr"/>
+      <c r="AE378" t="inlineStr"/>
+      <c r="AF378" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>[源氏物語] [25]</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8408d306-75c9-64c5-675e-116b8cde5a81.json</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>8408d306-75c9-64c5-675e-116b8cde5a81</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr"/>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/8408d306-75c9-64c5-675e-116b8cde5a81</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/48dd4df94091e413addb05c46ab2e5ddb045ff42.jpg</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381416</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr"/>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="Z379" t="inlineStr"/>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8408d306-75c9-64c5-675e-116b8cde5a81/manifest</t>
+        </is>
+      </c>
+      <c r="AB379" t="inlineStr"/>
+      <c r="AC379" t="inlineStr"/>
+      <c r="AD379" t="inlineStr"/>
+      <c r="AE379" t="inlineStr"/>
+      <c r="AF379" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>[源氏物語] [26]</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ゲンジ モノガタリ</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>A05:4</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>絵入本|無辺無界</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>[紫式部著]</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>林和泉掾</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>万治3年</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>和古書</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7a1f7f7a-8275-0590-9ff1-f5aa9adf831c.json</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>7a1f7f7a-8275-0590-9ff1-f5aa9adf831c</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/ogai/document/7a1f7f7a-8275-0590-9ff1-f5aa9adf831c</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/bc122665535d6898dc1c724e6745da8428f2cace.jpg</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1381415</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>東京大学総合図書館 General Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr"/>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>鷗外文庫書入本画像データベース</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr"/>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7a1f7f7a-8275-0590-9ff1-f5aa9adf831c/manifest</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr"/>
+      <c r="AC380" t="inlineStr"/>
+      <c r="AD380" t="inlineStr"/>
+      <c r="AE380" t="inlineStr"/>
+      <c r="AF380" t="n">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
